--- a/data/trans_orig/P36BPD08_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de vasos de vino que consumen a la semana en 2023</t>
+          <t>Población según el número de vasos de vino que consumen a la semana en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>386647</t>
+          <t>388283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>419466</t>
+          <t>419222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>731298</t>
+          <t>730334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>742735</t>
+          <t>742889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1120048</t>
+          <t>1122833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1157157</t>
+          <t>1157352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53296</t>
+          <t>52685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64350</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93156</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72097</t>
+          <t>70872</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102928</t>
+          <t>100772</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2003310</t>
+          <t>2001821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2123937</t>
+          <t>2114232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2147458</t>
+          <t>2146846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2184690</t>
+          <t>2183986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4162878</t>
+          <t>4159531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4276082</t>
+          <t>4273975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128448</t>
+          <t>130117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103207</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168355</t>
+          <t>169299</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91933</t>
+          <t>101464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168120</t>
+          <t>172452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>25185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140218</t>
+          <t>140330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209277</t>
+          <t>210653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>558199</t>
+          <t>559104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>590060</t>
+          <t>589595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>624807</t>
+          <t>624922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>641008</t>
+          <t>641069</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1190825</t>
+          <t>1190503</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1227123</t>
+          <t>1227346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>47181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62246</t>
+          <t>60539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>63621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2972621</t>
+          <t>2975744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3118211</t>
+          <t>3115778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3515798</t>
+          <t>3515905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3558142</t>
+          <t>3558393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6505334</t>
+          <t>6507557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6637212</t>
+          <t>6640718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122810</t>
+          <t>125067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196593</t>
+          <t>196769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46805</t>
+          <t>48472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>76208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184617</t>
+          <t>182970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257652</t>
+          <t>257581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192347</t>
+          <t>199477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>291555</t>
+          <t>291606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>69355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>266860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>349170</t>
+          <t>350927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD08_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>403776</t>
+          <t>458877</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388283</t>
+          <t>440015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>419222</t>
+          <t>476187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>737660</t>
+          <t>802872</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>730334</t>
+          <t>795830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>742889</t>
+          <t>808222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1141437</t>
+          <t>1261749</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1122833</t>
+          <t>1241331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1157352</t>
+          <t>1279898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40905</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52685</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64350</t>
+          <t>68660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92832</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>84649</t>
+          <t>89921</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>76217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100772</t>
+          <t>106441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>512520</t>
+          <t>576012</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512520</t>
+          <t>576012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>512520</t>
+          <t>576012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754469</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754469</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754469</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1266990</t>
+          <t>1396966</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266990</t>
+          <t>1396966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1266990</t>
+          <t>1396966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2046477</t>
+          <t>1968246</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2001821</t>
+          <t>1935972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2114232</t>
+          <t>2000495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2164349</t>
+          <t>2085098</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2146846</t>
+          <t>2069834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2183986</t>
+          <t>2100858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4210826</t>
+          <t>4053344</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4159531</t>
+          <t>4011938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4273975</t>
+          <t>4089000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>98706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>77519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130117</t>
+          <t>124271</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>53755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>134752</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>114906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>169299</t>
+          <t>169763</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>141118</t>
+          <t>158099</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101464</t>
+          <t>133588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172452</t>
+          <t>181473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>177166</t>
+          <t>201233</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140330</t>
+          <t>175415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210653</t>
+          <t>230998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2285083</t>
+          <t>2225051</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2285083</t>
+          <t>2225051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2285083</t>
+          <t>2225051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237661</t>
+          <t>2170326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4522744</t>
+          <t>4395377</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4522744</t>
+          <t>4395377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4522744</t>
+          <t>4395377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>576321</t>
+          <t>634859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>559104</t>
+          <t>618086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>589595</t>
+          <t>651700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>633463</t>
+          <t>704214</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>624922</t>
+          <t>694683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>641069</t>
+          <t>712442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1209785</t>
+          <t>1339073</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1190503</t>
+          <t>1318164</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1227346</t>
+          <t>1357392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47181</t>
+          <t>47238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21288</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>64931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49778</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645949</t>
+          <t>710859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645949</t>
+          <t>710859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645949</t>
+          <t>710859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659805</t>
+          <t>734199</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659805</t>
+          <t>734199</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659805</t>
+          <t>734199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305754</t>
+          <t>1445058</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305754</t>
+          <t>1445058</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305754</t>
+          <t>1445058</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3026574</t>
+          <t>3061982</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2975744</t>
+          <t>3021654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3115778</t>
+          <t>3102676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3535472</t>
+          <t>3592185</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3515905</t>
+          <t>3571974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3558393</t>
+          <t>3610762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6562047</t>
+          <t>6654166</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6507557</t>
+          <t>6607331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6640718</t>
+          <t>6698311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>166761</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125067</t>
+          <t>142009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196769</t>
+          <t>195601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48472</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76208</t>
+          <t>83546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>221848</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182970</t>
+          <t>208776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257581</t>
+          <t>270859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>256586</t>
+          <t>283179</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199477</t>
+          <t>255906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>291606</t>
+          <t>317472</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>51796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>311593</t>
+          <t>347117</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>266860</t>
+          <t>312161</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>350927</t>
+          <t>384045</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3443552</t>
+          <t>3511922</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3443552</t>
+          <t>3511922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3443552</t>
+          <t>3511922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3651935</t>
+          <t>3725480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3651935</t>
+          <t>3725480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3651935</t>
+          <t>3725480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7095488</t>
+          <t>7237401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7095488</t>
+          <t>7237401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7095488</t>
+          <t>7237401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
